--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitionerrole</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitionerrole</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T12:29:31+00:00</t>
+    <t>2023-06-02T14:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -354,7 +354,7 @@
     <t>as-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
 </t>
   </si>
   <si>
@@ -613,7 +613,7 @@
     <t>as-ext-practitionerrole-name</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-name}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-name}
 </t>
   </si>
   <si>
@@ -632,7 +632,7 @@
     <t>as-ext-practitionerrole-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration}
 </t>
   </si>
   <si>
@@ -651,7 +651,7 @@
     <t>as-ext-practitionerrole-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level}
 </t>
   </si>
   <si>
@@ -667,7 +667,7 @@
     <t>as-ext-practitionerrole-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-smartcard}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-smartcard}
 </t>
   </si>
   <si>
@@ -687,7 +687,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
 </t>
   </si>
   <si>
@@ -1002,7 +1002,7 @@
     <t>PractitionerRole.extension.url</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-digital-certificate.value[x]</t>
@@ -1021,7 +1021,7 @@
     <t>as-ext-practitionerrole-end-cause</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-end-cause}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-end-cause}
 </t>
   </si>
   <si>
@@ -1040,7 +1040,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted}
 </t>
   </si>
   <si>
@@ -1059,7 +1059,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas}
 </t>
   </si>
   <si>
@@ -1078,7 +1078,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted}
 </t>
   </si>
   <si>
@@ -1673,7 +1673,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
 </t>
   </si>
   <si>
@@ -1932,7 +1932,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
 </t>
   </si>
   <si>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T14:39:58+00:00</t>
+    <t>2023-06-02T15:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
